--- a/Golf League Data.xlsx
+++ b/Golf League Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gensl\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCE1FBA6-39EF-4514-8CEB-9E380D562FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD56C3CD-670F-4055-BE10-928A22D13057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30680507-2CB2-4D12-B50F-3BB9703B41B0}"/>
   </bookViews>
@@ -16,7 +16,11 @@
     <sheet name="Historical Scores" sheetId="1" r:id="rId1"/>
     <sheet name="Scorecards" sheetId="2" r:id="rId2"/>
     <sheet name="Handicap" sheetId="3" r:id="rId3"/>
+    <sheet name="Members" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historical Scores'!$A$1:$O$1016</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3641" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3657" uniqueCount="95">
   <si>
     <t>Golfer Name</t>
   </si>
@@ -741,6 +745,7 @@
   <dimension ref="A1:O1016"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -45632,6 +45637,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O1016" xr:uid="{5EEBB3BC-6E1E-4767-A1BC-7ECF02F8BCAA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -50531,4 +50537,97 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C69D8205-593F-4C24-96A4-7408DC96481B}">
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>